--- a/documentation/calibration/calibration-group2.xlsx
+++ b/documentation/calibration/calibration-group2.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://heriotwatt-my.sharepoint.com/personal/ts2104_hw_ac_uk/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://heriotwatt-my.sharepoint.com/personal/ts2104_hw_ac_uk/Documents/Github/System-Project-G2/documentation/calibration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="8_{BE8412CD-7915-4FAA-8293-D30577E33BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19044216-CE5A-435B-A044-402499D31976}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{BE8412CD-7915-4FAA-8293-D30577E33BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A991B56-0AFD-47F7-8E7B-C6459017C959}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="20602" windowHeight="12097" xr2:uid="{A5972991-0E36-4B95-B7E7-E22FB6D328CD}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="20602" windowHeight="12097" activeTab="1" xr2:uid="{A5972991-0E36-4B95-B7E7-E22FB6D328CD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Motors" sheetId="1" r:id="rId1"/>
+    <sheet name="Ultrasonic" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>Min Blinks</t>
   </si>
@@ -84,6 +85,27 @@
   </si>
   <si>
     <t>Battery at 3 bars</t>
+  </si>
+  <si>
+    <t>US Length</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>(cm)</t>
+  </si>
+  <si>
+    <t>not reliable</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>metal</t>
+  </si>
+  <si>
+    <t>big object</t>
   </si>
 </sst>
 </file>
@@ -728,4 +750,185 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8E08DA-A2CB-44C6-A8F0-868B0B99C4BA}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>30</v>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>40</v>
+      </c>
+      <c r="C8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>50</v>
+      </c>
+      <c r="C9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>60</v>
+      </c>
+      <c r="C10">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>70</v>
+      </c>
+      <c r="C11">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>80</v>
+      </c>
+      <c r="C12">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>90</v>
+      </c>
+      <c r="C13">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>100</v>
+      </c>
+      <c r="C14">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>150</v>
+      </c>
+      <c r="B16">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>200</v>
+      </c>
+      <c r="B17">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>250</v>
+      </c>
+      <c r="B18">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>300</v>
+      </c>
+      <c r="B19">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>350</v>
+      </c>
+      <c r="B20">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>400</v>
+      </c>
+      <c r="B21">
+        <v>392</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/documentation/calibration/calibration-group2.xlsx
+++ b/documentation/calibration/calibration-group2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://heriotwatt-my.sharepoint.com/personal/ts2104_hw_ac_uk/Documents/Github/System-Project-G2/documentation/calibration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="8_{BE8412CD-7915-4FAA-8293-D30577E33BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A991B56-0AFD-47F7-8E7B-C6459017C959}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="8_{BE8412CD-7915-4FAA-8293-D30577E33BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E42D5B0D-2A4B-572D-A0A2-DA7CA9A4E7DD}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="735" windowWidth="20602" windowHeight="12097" activeTab="1" xr2:uid="{A5972991-0E36-4B95-B7E7-E22FB6D328CD}"/>
   </bookViews>
